--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121745772</v>
       </c>
       <c r="B3" t="n">
-        <v>109993</v>
+        <v>110011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121745772</v>
       </c>
       <c r="B3" t="n">
-        <v>110011</v>
+        <v>110013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121745772</v>
       </c>
       <c r="B3" t="n">
-        <v>110013</v>
+        <v>110020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121745772</v>
       </c>
       <c r="B3" t="n">
-        <v>110020</v>
+        <v>110029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,122 +799,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>121745772</v>
-      </c>
-      <c r="B3" t="n">
-        <v>110037</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Valeriana dioica</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Stenestad, öster, Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>409739</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6215598</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Höör</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Norra Rörum</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Hör-0190</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Carl-Axel Andersson, Ole Tryggeson, Johnny Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>86039593</v>
       </c>
       <c r="B2" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409738.9500505569</v>
+        <v>409739</v>
       </c>
       <c r="R2" t="n">
-        <v>6215597.756998139</v>
+        <v>6215598</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 48926-2024 artfynd.xlsx
+++ b/artfynd/A 48926-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,8 +788,16 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86039593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>